--- a/ns-3.45/result_csv/cu_0125_1st.xlsx
+++ b/ns-3.45/result_csv/cu_0125_1st.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BFBF2CB-178B-114B-A807-A8BCEEAC4C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9432C759-3264-E94E-9D83-1DDCC75E5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1800" windowWidth="28300" windowHeight="17360" xr2:uid="{577C6F03-6641-F047-869B-910FBDE743F8}"/>
   </bookViews>
   <sheets>
     <sheet name="cu_0125_1st" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>Stations</t>
   </si>
@@ -86,6 +99,10 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>predict</t>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -738,6 +755,380 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_1st!$V$2:$V$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>87.041200000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>89.373500000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.640600000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90.147599999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>90.0184</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>89.645899999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>89.588300000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.867699999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>81.075900000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-29B5-5649-948F-12301EBD19CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>cu_0125_1st!$U$2:$U$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>87.170902146506577</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.437307005560172</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67.437127739080097</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86.244446642403631</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>67.113906849769592</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>79.870845403870916</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>88.293187984899831</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>88.429707306157212</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>68.357662805751829</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>68.517702595733411</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-29B5-5649-948F-12301EBD19CE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="911480959"/>
+        <c:axId val="911489023"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="911480959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="911489023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="911489023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="911480959"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>908050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>717550</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45F0A061-6E83-4ABF-D460-484305E07903}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1057,10 +1448,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1289526-EF2B-C241-9381-B9DD443BCF26}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1121,8 +1512,11 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>29</v>
       </c>
@@ -1183,8 +1577,15 @@
       <c r="T2">
         <v>23.608699999999999</v>
       </c>
+      <c r="U2">
+        <f>88.635042*(1-EXP(-(-0.005187*C2-0.006152*S2+0.216919*A2-0.48788)))</f>
+        <v>87.170902146506577</v>
+      </c>
+      <c r="V2">
+        <v>87.041200000000003</v>
+      </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>41</v>
       </c>
@@ -1245,8 +1646,15 @@
       <c r="T3">
         <v>14.741400000000001</v>
       </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="0">88.635042*(1-EXP(-(-0.005187*C3-0.006152*S3+0.216919*A3-0.48788)))</f>
+        <v>88.437307005560172</v>
+      </c>
+      <c r="V3">
+        <v>89.875</v>
+      </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>12</v>
       </c>
@@ -1307,8 +1715,15 @@
       <c r="T4">
         <v>28.571300000000001</v>
       </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>67.437127739080097</v>
+      </c>
+      <c r="V4">
+        <v>89.373500000000007</v>
+      </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>44</v>
       </c>
@@ -1369,8 +1784,15 @@
       <c r="T5">
         <v>10.738200000000001</v>
       </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>86.244446642403631</v>
+      </c>
+      <c r="V5">
+        <v>88.640600000000006</v>
+      </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>12</v>
       </c>
@@ -1431,8 +1853,15 @@
       <c r="T6">
         <v>31.195399999999999</v>
       </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>67.113906849769592</v>
+      </c>
+      <c r="V6">
+        <v>90.147599999999997</v>
+      </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>22</v>
       </c>
@@ -1493,8 +1922,15 @@
       <c r="T7">
         <v>38.556699999999999</v>
       </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>79.870845403870916</v>
+      </c>
+      <c r="V7">
+        <v>90.0184</v>
+      </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>35</v>
       </c>
@@ -1555,8 +1991,15 @@
       <c r="T8">
         <v>16.766300000000001</v>
       </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>88.293187984899831</v>
+      </c>
+      <c r="V8">
+        <v>89.645899999999997</v>
+      </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>38</v>
       </c>
@@ -1617,8 +2060,15 @@
       <c r="T9">
         <v>11.404400000000001</v>
       </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>88.429707306157212</v>
+      </c>
+      <c r="V9">
+        <v>89.588300000000004</v>
+      </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>13</v>
       </c>
@@ -1679,8 +2129,15 @@
       <c r="T10">
         <v>52.888399999999997</v>
       </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>68.357662805751829</v>
+      </c>
+      <c r="V10">
+        <v>88.867699999999999</v>
+      </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1740,10 +2197,18 @@
       </c>
       <c r="T11">
         <v>9.5522600000000004</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>68.517702595733411</v>
+      </c>
+      <c r="V11">
+        <v>81.075900000000004</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/ns-3.45/result_csv/cu_0125_1st.xlsx
+++ b/ns-3.45/result_csv/cu_0125_1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9432C759-3264-E94E-9D83-1DDCC75E5A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A1779-4836-FF41-AA3D-C3A56ABA869C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="1800" windowWidth="28300" windowHeight="17360" xr2:uid="{577C6F03-6641-F047-869B-910FBDE743F8}"/>
+    <workbookView xWindow="5040" yWindow="1800" windowWidth="30800" windowHeight="17360" xr2:uid="{577C6F03-6641-F047-869B-910FBDE743F8}"/>
   </bookViews>
   <sheets>
     <sheet name="cu_0125_1st" sheetId="1" r:id="rId1"/>
@@ -772,6 +772,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>ランダム実行</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ja-JP"/>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ja-JP" altLang="en-US"/>
+              <a:t>回分の比較</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -780,26 +813,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -810,6 +823,9 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>calcurated</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100">
               <a:noFill/>
@@ -817,7 +833,7 @@
           </c:spPr>
           <c:yVal>
             <c:numRef>
-              <c:f>cu_0125_1st!$V$2:$V$11</c:f>
+              <c:f>cu_0125_1st!$I$2:$I$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -864,6 +880,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>measured</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:noFill/>
@@ -893,31 +912,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>87.170902146506577</c:v>
+                  <c:v>88.783260362183327</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>88.437307005560172</c:v>
+                  <c:v>89.727888440490176</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>67.437127739080097</c:v>
+                  <c:v>82.54064556770345</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.244446642403631</c:v>
+                  <c:v>89.832088930385467</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67.113906849769592</c:v>
+                  <c:v>82.20773551838144</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>79.870845403870916</c:v>
+                  <c:v>87.919712392923444</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>88.293187984899831</c:v>
+                  <c:v>89.181923810770996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>88.429707306157212</c:v>
+                  <c:v>89.470194104526541</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>68.357662805751829</c:v>
+                  <c:v>83.038318058395319</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>68.517702595733411</c:v>
@@ -964,6 +983,24 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>実行</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1025,6 +1062,24 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1067,6 +1122,10 @@
         <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1102,8 +1161,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>717550</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1578,8 +1637,8 @@
         <v>23.608699999999999</v>
       </c>
       <c r="U2">
-        <f>88.635042*(1-EXP(-(-0.005187*C2-0.006152*S2+0.216919*A2-0.48788)))</f>
-        <v>87.170902146506577</v>
+        <f>90.295154*(1-EXP(-(0.014527*J2-0.004408*S2+0.117353*A2-0.377617)))</f>
+        <v>88.783260362183327</v>
       </c>
       <c r="V2">
         <v>87.041200000000003</v>
@@ -1647,8 +1706,8 @@
         <v>14.741400000000001</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U11" si="0">88.635042*(1-EXP(-(-0.005187*C3-0.006152*S3+0.216919*A3-0.48788)))</f>
-        <v>88.437307005560172</v>
+        <f t="shared" ref="U3:U10" si="0">90.295154*(1-EXP(-(0.014527*J3-0.004408*S3+0.117353*A3-0.377617)))</f>
+        <v>89.727888440490176</v>
       </c>
       <c r="V3">
         <v>89.875</v>
@@ -1717,7 +1776,7 @@
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>67.437127739080097</v>
+        <v>82.54064556770345</v>
       </c>
       <c r="V4">
         <v>89.373500000000007</v>
@@ -1786,7 +1845,7 @@
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>86.244446642403631</v>
+        <v>89.832088930385467</v>
       </c>
       <c r="V5">
         <v>88.640600000000006</v>
@@ -1855,7 +1914,7 @@
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>67.113906849769592</v>
+        <v>82.20773551838144</v>
       </c>
       <c r="V6">
         <v>90.147599999999997</v>
@@ -1924,7 +1983,7 @@
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>79.870845403870916</v>
+        <v>87.919712392923444</v>
       </c>
       <c r="V7">
         <v>90.0184</v>
@@ -1993,7 +2052,7 @@
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>88.293187984899831</v>
+        <v>89.181923810770996</v>
       </c>
       <c r="V8">
         <v>89.645899999999997</v>
@@ -2062,7 +2121,7 @@
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>88.429707306157212</v>
+        <v>89.470194104526541</v>
       </c>
       <c r="V9">
         <v>89.588300000000004</v>
@@ -2131,7 +2190,7 @@
       </c>
       <c r="U10">
         <f t="shared" si="0"/>
-        <v>68.357662805751829</v>
+        <v>83.038318058395319</v>
       </c>
       <c r="V10">
         <v>88.867699999999999</v>
@@ -2199,7 +2258,7 @@
         <v>9.5522600000000004</v>
       </c>
       <c r="U11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U3:U11" si="1">88.635042*(1-EXP(-(-0.005187*C11-0.006152*S11+0.216919*A11-0.48788)))</f>
         <v>68.517702595733411</v>
       </c>
       <c r="V11">
